--- a/data/trans_orig/IP09-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP09-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5879</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8023</t>
+          <t>7945</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>3885</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11410</t>
+          <t>11156</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>43,69%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>4044</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>8989</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>7585</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13525</t>
+          <t>13021</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14125</t>
+          <t>14379</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21519</t>
+          <t>21650</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,78%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7748</t>
+          <t>7762</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3955</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12067</t>
+          <t>12348</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7218</t>
+          <t>7059</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16955</t>
+          <t>16852</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16917</t>
+          <t>16903</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23362</t>
+          <t>22879</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23074</t>
+          <t>22793</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31186</t>
+          <t>31055</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>42851</t>
+          <t>42954</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>52588</t>
+          <t>52747</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,2%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6581</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9554</t>
+          <t>9743</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13868</t>
+          <t>13838</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,15%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7118</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12368</t>
+          <t>12364</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5484</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11638</t>
+          <t>11723</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14869</t>
+          <t>14899</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>22861</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,55%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>621</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3279</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9332</t>
+          <t>9289</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5098</t>
+          <t>4541</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12588</t>
+          <t>12355</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>48,18%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>2821</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7268</t>
+          <t>7253</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8437</t>
+          <t>8480</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14490</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13055</t>
+          <t>13288</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20545</t>
+          <t>21102</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>82,29%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18823</t>
+          <t>18927</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17885</t>
+          <t>18238</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31518</t>
+          <t>31815</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28746</t>
+          <t>28478</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45033</t>
+          <t>46224</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37420</t>
+          <t>37316</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47692</t>
+          <t>48008</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51960</t>
+          <t>51663</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>65593</t>
+          <t>65240</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>94688</t>
+          <t>93497</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>110975</t>
+          <t>111243</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,62%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10944</t>
+          <t>10420</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11348</t>
+          <t>11245</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9635</t>
+          <t>9475</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19931</t>
+          <t>19557</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>42,56%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10064</t>
+          <t>10588</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17008</t>
+          <t>17038</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13591</t>
+          <t>13694</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20936</t>
+          <t>20979</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26016</t>
+          <t>26390</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36312</t>
+          <t>36472</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,38%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>5433</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13180</t>
+          <t>13944</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14712</t>
+          <t>15043</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12839</t>
+          <t>13094</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25568</t>
+          <t>25621</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,41%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15108</t>
+          <t>14344</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23099</t>
+          <t>22855</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23709</t>
+          <t>23378</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32983</t>
+          <t>32671</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>41141</t>
+          <t>41088</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>53870</t>
+          <t>53615</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,37%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10798</t>
+          <t>10950</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7056</t>
+          <t>7087</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6315</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15672</t>
+          <t>15978</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>45,44%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9401</t>
+          <t>9249</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16688</t>
+          <t>16354</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7905</t>
+          <t>7874</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13576</t>
+          <t>13539</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19488</t>
+          <t>19182</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28845</t>
+          <t>28275</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>80,42%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>8779</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9076</t>
+          <t>8747</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17438</t>
+          <t>16837</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13746</t>
+          <t>14180</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23742</t>
+          <t>23752</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,38%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4794</t>
+          <t>4596</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10635</t>
+          <t>10627</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6660</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15022</t>
+          <t>15351</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13731</t>
+          <t>13721</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23727</t>
+          <t>23293</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>62,16%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22240</t>
+          <t>22023</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35877</t>
+          <t>35934</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26651</t>
+          <t>26828</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42342</t>
+          <t>42523</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52464</t>
+          <t>53194</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74221</t>
+          <t>74540</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,23%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46992</t>
+          <t>46935</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60629</t>
+          <t>60846</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60077</t>
+          <t>59896</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75768</t>
+          <t>75591</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>111068</t>
+          <t>110749</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>132825</t>
+          <t>132095</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,29%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2521</t>
+          <t>2423</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7352</t>
+          <t>7286</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>5643</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11906</t>
+          <t>11747</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>52,65%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>7259</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>6988</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11580</t>
+          <t>11530</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>10566</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17856</t>
+          <t>17758</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>79,58%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>3370</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9642</t>
+          <t>10025</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7412</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15352</t>
+          <t>15108</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13365</t>
+          <t>12989</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22776</t>
+          <t>23473</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>59,3%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8874</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15325</t>
+          <t>15146</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5717</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13657</t>
+          <t>13392</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16809</t>
+          <t>16112</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26220</t>
+          <t>26596</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>67,19%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>5987</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2249</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>4858</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11011</t>
+          <t>11032</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,1%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2524</t>
+          <t>2392</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7143</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3278</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9643</t>
+          <t>9452</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>66,05%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2236</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>7580</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12724</t>
+          <t>13323</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>59,58%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>4236</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9657</t>
+          <t>9722</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9637</t>
+          <t>9038</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16964</t>
+          <t>16815</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,2%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13716</t>
+          <t>13995</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24245</t>
+          <t>24775</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17685</t>
+          <t>18024</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29248</t>
+          <t>29737</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34396</t>
+          <t>35470</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50248</t>
+          <t>51558</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>52,31%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22878</t>
+          <t>22348</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33407</t>
+          <t>33128</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22199</t>
+          <t>21710</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33762</t>
+          <t>33423</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48322</t>
+          <t>47012</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>64174</t>
+          <t>63100</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>64,01%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>754</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>6406</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>2790</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6907</t>
+          <t>6653</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6903</t>
+          <t>7575</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12075</t>
+          <t>12450</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17800</t>
+          <t>17670</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>93,71%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2563</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7011</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12128</t>
+          <t>11987</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8615</t>
+          <t>9142</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17577</t>
+          <t>17411</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>54,5%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6729</t>
+          <t>6667</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10531</t>
+          <t>10672</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17772</t>
+          <t>17932</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14373</t>
+          <t>14539</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23335</t>
+          <t>22808</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>71,39%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11347</t>
+          <t>11313</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5822</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14916</t>
+          <t>14725</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>11884</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23116</t>
+          <t>24001</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>59,75%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12422</t>
+          <t>12581</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8513</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17607</t>
+          <t>18022</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17051</t>
+          <t>16166</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28269</t>
+          <t>28283</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,41%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>3161</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18675</t>
+          <t>19252</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>4210</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18030</t>
+          <t>18530</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>10496</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33674</t>
+          <t>31841</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10671</t>
+          <t>10094</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26652</t>
+          <t>26185</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23462</t>
+          <t>22962</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37724</t>
+          <t>37282</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37164</t>
+          <t>38997</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59938</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>85,18%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17385</t>
+          <t>17052</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37000</t>
+          <t>35165</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18953</t>
+          <t>19946</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>39888</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41883</t>
+          <t>39976</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70448</t>
+          <t>69126</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>42,72%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25782</t>
+          <t>27617</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45397</t>
+          <t>45730</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60111</t>
+          <t>59141</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>80076</t>
+          <t>79083</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>91363</t>
+          <t>92685</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>119928</t>
+          <t>121835</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>75,29%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP09-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP09-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4594</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7917</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>29,58%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>12,73%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>50,98%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2949</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1016</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5961</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5431</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>29,48%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,16%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>59,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4594</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2509</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7945</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>29,58%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11156</t>
+          <t>11405</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>44,66%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10936</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7613</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13553</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>70,42%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>49,02%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>87,27%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>7056</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4044</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8989</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4574</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>9313</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>70,52%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>40,42%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>89,84%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>10936</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>7585</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>13021</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>70,42%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14379</t>
+          <t>14130</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21650</t>
+          <t>21425</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>83,9%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15530</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15530</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>15530</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>10005</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>10005</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>10005</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>15530</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>15530</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>15530</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7400</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4111</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12028</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>21,06%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>11,7%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>34,23%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3945</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1786</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7762</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1772</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8669</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>16,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,24%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>31,47%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>7400</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4086</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>12348</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>21,06%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7059</t>
+          <t>6949</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16852</t>
+          <t>16932</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,31%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>27741</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>23113</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>31030</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>78,94%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>65,77%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>88,3%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>20720</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>16903</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22879</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>15996</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>22893</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>84,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>68,53%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>92,76%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>27741</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>22793</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>31055</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>78,94%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>42954</t>
+          <t>42874</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>52747</t>
+          <t>52857</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,38%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>35141</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>35141</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>35141</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>24665</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>24665</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>24665</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>35141</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>35141</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>35141</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6151</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3320</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9563</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>40,9%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>22,08%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>63,59%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3427</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1335</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6710</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1308</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6374</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>25,02%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,75%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>48,98%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6151</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3315</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9743</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>40,9%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>5457</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13838</t>
+          <t>14198</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>49,41%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8887</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5475</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>11718</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>59,1%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>36,41%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>77,92%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>10272</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>6989</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>12364</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>7325</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>12391</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>74,98%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>51,02%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>90,25%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>8887</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>5295</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>11723</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>59,1%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14899</t>
+          <t>14539</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22861</t>
+          <t>23280</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>81,01%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15038</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15038</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15038</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>13699</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>13699</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>13699</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>15038</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>15038</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>15038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5896</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3236</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9769</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>33,18%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>18,21%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>54,98%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2479</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5053</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5163</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>31,48%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,89%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>64,18%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5896</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3251</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9289</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>33,18%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12355</t>
+          <t>12281</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>47,89%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11873</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14533</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>66,82%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>45,02%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>81,79%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>5395</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2821</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7253</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2711</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>7230</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>68,52%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>35,82%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,11%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>11873</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>8480</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>14518</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>66,82%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13288</t>
+          <t>13362</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21102</t>
+          <t>20561</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>80,18%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>17769</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>17769</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>17769</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>7874</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>7874</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>7874</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>17769</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>17769</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>17769</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>24042</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18092</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>30739</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>28,8%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>21,67%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>36,82%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>12800</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>8235</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>18927</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>8067</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>18237</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>22,76%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>14,64%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>33,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>24042</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>18238</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>31815</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>28,8%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28478</t>
+          <t>29266</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46224</t>
+          <t>46196</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>59436</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>52739</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>65386</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>71,2%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>63,18%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>78,33%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>43443</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>37316</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>48008</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>38006</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>48176</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>77,24%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>66,35%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>85,36%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>59436</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>51663</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>65240</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>71,2%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>93497</t>
+          <t>93525</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>111243</t>
+          <t>110455</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,05%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>83478</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>83478</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>83478</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>56243</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>56243</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>56243</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>83478</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>83478</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>83478</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7344</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3876</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11589</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>29,45%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>15,54%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>46,47%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6942</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3970</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10420</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3780</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10641</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>33,05%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>18,9%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>49,6%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7344</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3960</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11245</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>29,45%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9475</t>
+          <t>9525</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19557</t>
+          <t>20254</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>44,08%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17595</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13350</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21063</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>70,55%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>53,53%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>84,46%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>14066</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10588</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17038</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10367</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>17228</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>66,95%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>50,4%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>81,1%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>17595</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>13694</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>20979</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>70,55%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26390</t>
+          <t>25693</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36472</t>
+          <t>36422</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,27%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24939</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24939</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24939</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>21008</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>21008</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>21008</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>24939</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>24939</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>24939</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3018,67 +3018,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>9767</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5566</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14680</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>25,42%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14,49%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>38,21%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>8960</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5433</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>13944</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>5320</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>13406</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>31,67%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>19,21%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>49,29%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9767</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5750</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>15043</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>25,42%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13094</t>
+          <t>12966</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25621</t>
+          <t>24996</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>37,47%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28654</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>23741</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>32855</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>74,58%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>61,79%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>85,51%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>19328</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>14344</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22855</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>14882</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>22968</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>68,33%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>50,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>80,79%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>28654</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>23378</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>32671</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>74,58%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>41088</t>
+          <t>41713</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>53615</t>
+          <t>53743</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,56%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>38421</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>38421</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>38421</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>28288</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>28288</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>28288</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>38421</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>38421</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>38421</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3778</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1365</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6815</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>25,26%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9,12%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>45,55%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>7013</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3845</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10950</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3680</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11140</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>34,72%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,03%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>54,21%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3778</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1422</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7087</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>25,26%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15978</t>
+          <t>16030</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,59%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11183</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8146</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>13596</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>74,74%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>54,45%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>90,88%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>13186</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9249</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>16354</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>16519</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>65,28%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>45,79%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>80,97%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>11183</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>7874</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>13539</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>74,74%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19182</t>
+          <t>19130</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28275</t>
+          <t>28053</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>79,79%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14961</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>14961</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>14961</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>20199</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>20199</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>20199</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>14961</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>14961</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>14961</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13362</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8765</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>17064</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>55,45%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>36,37%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>70,81%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>5482</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2748</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8779</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2752</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8393</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>40,99%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>20,55%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>65,64%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>13362</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>8747</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>16837</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>55,45%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14180</t>
+          <t>13866</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23752</t>
+          <t>23608</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,0%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10736</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7034</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15333</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>44,55%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>29,19%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>63,63%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>7893</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>4596</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10627</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>4982</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>10623</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>59,01%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>34,36%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>79,45%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>10736</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>7261</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>15351</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>44,55%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13721</t>
+          <t>13865</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23293</t>
+          <t>23607</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>63,0%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>24098</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>24098</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>24098</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>13375</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>13375</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>13375</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>24098</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>24098</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>24098</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>34252</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>26680</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>43680</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>33,44%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>26,05%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>42,65%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>28397</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>22023</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>35934</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>21589</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>35499</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>34,27%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>26,58%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>43,36%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>34252</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>26828</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>42523</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>33,44%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53194</t>
+          <t>53598</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74540</t>
+          <t>74753</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,34%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>68167</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>58739</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>75739</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>66,56%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>57,35%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>73,95%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>54472</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>46935</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>60846</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>47370</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>61280</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>65,73%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>56,64%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>73,42%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>68167</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>59896</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>75591</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>66,56%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>110749</t>
+          <t>110536</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>132095</t>
+          <t>131691</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,07%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>102419</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>102419</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>102419</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>82869</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>82869</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>82869</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>102419</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>102419</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>102419</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1125</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5985</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>23,76%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8,91%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>47,39%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4854</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2423</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7286</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2461</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7210</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>50,14%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>25,02%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>75,25%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3001</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5643</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>23,76%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>4741</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11747</t>
+          <t>11794</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,86%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9630</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6646</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11506</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>76,24%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>52,61%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>91,09%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>4828</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2396</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7259</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7221</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>49,86%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>24,75%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>74,98%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>9630</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>6988</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>11530</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>76,24%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10566</t>
+          <t>10519</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17758</t>
+          <t>17572</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>78,75%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12631</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12631</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12631</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>9682</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>9682</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>9682</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>12631</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>12631</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>12631</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11709</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7772</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>15410</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>55,57%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>36,89%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>73,14%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>6197</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3370</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10025</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3414</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9921</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>33,47%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18,2%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>54,14%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>11709</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7677</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>15108</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>55,57%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12989</t>
+          <t>13008</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23473</t>
+          <t>22741</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>57,45%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9360</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5659</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13297</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>44,43%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>26,86%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>63,11%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>12319</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8491</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>15146</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>8595</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>66,53%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>45,86%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>81,8%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>9360</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>5961</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>13392</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>44,43%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16112</t>
+          <t>16844</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26596</t>
+          <t>26577</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,14%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>21069</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>21069</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>21069</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>18516</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>18516</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>18516</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>21069</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>21069</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>21069</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4535</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2288</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5931</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>76,45%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>38,57%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3337</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1164</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5987</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5893</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>39,83%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>71,45%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4535</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2270</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5931</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>76,45%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4858</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11032</t>
+          <t>10911</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>76,25%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1396</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3643</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>23,55%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>61,43%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>5042</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2392</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7215</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2486</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>7161</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>60,17%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>28,55%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>86,11%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1396</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>3661</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>23,55%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9452</t>
+          <t>9555</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>66,77%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5931</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5931</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5931</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>8379</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>8379</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>8379</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>5931</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>5931</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>5931</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4531</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2156</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7616</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>38,34%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>18,24%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>64,46%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>4688</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2236</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7538</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2079</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7513</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>44,46%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>21,21%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>71,48%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4531</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2094</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7580</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>38,34%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13323</t>
+          <t>13586</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>60,76%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7285</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4200</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9660</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>61,66%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>35,54%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>81,76%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>5857</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3007</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8309</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3032</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>8466</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>55,54%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>28,52%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>78,79%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>7285</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>4236</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>9722</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>61,66%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9038</t>
+          <t>8775</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16815</t>
+          <t>16812</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,18%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>11816</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>11816</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>11816</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>10545</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>10545</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>10545</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>11816</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>11816</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>11816</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>23775</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18195</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>29911</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>46,21%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>35,37%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>58,14%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>19077</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>13995</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>24775</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>13988</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>24681</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>40,48%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>29,7%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>52,57%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>23775</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>18024</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>29737</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>46,21%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35470</t>
+          <t>35337</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51558</t>
+          <t>51256</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,0%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>27672</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>21536</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>33252</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>53,79%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>41,86%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>64,63%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>28046</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>22348</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>33128</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>22442</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>33135</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>59,52%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>47,43%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>70,3%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>27672</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>21710</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>33423</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>53,79%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47012</t>
+          <t>47314</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63100</t>
+          <t>63233</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>64,15%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>47123</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>47123</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>47123</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3509</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8,99%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>37,33%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2049</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>754</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4617</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>27,66%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,18%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>62,33%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>552</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>2762</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>844</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6406</t>
+          <t>5638</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,43%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8556</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5892</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9401</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>91,01%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>62,67%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5358</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2790</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6653</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>72,34%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>37,67%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>89,82%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10421</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7575</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>15779</t>
+          <t>13613</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12450</t>
+          <t>10737</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17670</t>
+          <t>15531</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>94,85%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9401</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9401</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9401</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>7407</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7407</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7407</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>18856</t>
+          <t>16375</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18856</t>
+          <t>16375</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18856</t>
+          <t>16375</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6983</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4029</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10274</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>36,94%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>21,31%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>54,35%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4795</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2625</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7062</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>51,61%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>28,25%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>76,0%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>2466</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11987</t>
+          <t>7031</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>13072</t>
+          <t>11584</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9142</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17411</t>
+          <t>15635</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>56,26%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11920</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8629</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14874</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>63,06%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>45,65%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>78,69%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4497</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2230</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6667</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>48,39%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>24,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>71,75%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14382</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10672</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17932</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>18878</t>
+          <t>16208</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14539</t>
+          <t>12157</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22808</t>
+          <t>20047</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>72,13%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>18903</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>18903</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>18903</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>9292</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>9292</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>9292</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22659</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22659</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22659</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>31950</t>
+          <t>27792</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>31950</t>
+          <t>27792</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>31950</t>
+          <t>27792</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9523</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5417</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13907</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>44,19%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>25,13%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>64,53%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7716</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4157</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11313</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>46,1%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>24,83%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>67,59%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9801</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14725</t>
+          <t>11724</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>17517</t>
+          <t>17383</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11884</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24001</t>
+          <t>23119</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,87%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12028</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>7644</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>16134</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>55,81%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>35,47%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>74,87%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>9022</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>5425</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>12581</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>53,9%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>32,41%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>75,17%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13628</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18022</t>
+          <t>12678</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>22650</t>
+          <t>21236</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16166</t>
+          <t>15500</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28283</t>
+          <t>26422</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>68,42%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>21551</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>21551</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>21551</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>16738</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>16738</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>16738</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23429</t>
+          <t>17068</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23429</t>
+          <t>17068</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23429</t>
+          <t>17068</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>40167</t>
+          <t>38619</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>40167</t>
+          <t>38619</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40167</t>
+          <t>38619</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10330</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16825</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>26,48%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,52%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>43,12%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>9341</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3161</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>19252</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>31,83%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,77%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>65,6%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10495</t>
+          <t>4733</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18530</t>
+          <t>8857</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>19836</t>
+          <t>15063</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10496</t>
+          <t>8672</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31841</t>
+          <t>23211</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>36,07%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>28686</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>22191</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>34910</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>73,52%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>56,88%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,48%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>20005</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>10094</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>26185</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>68,17%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>34,4%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>89,23%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>30997</t>
+          <t>20604</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22962</t>
+          <t>16480</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37282</t>
+          <t>23408</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>51002</t>
+          <t>49290</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38997</t>
+          <t>41142</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>60342</t>
+          <t>55681</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>86,52%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>39016</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>39016</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>39016</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>29346</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>29346</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>29346</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41492</t>
+          <t>25337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41492</t>
+          <t>25337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>41492</t>
+          <t>25337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>70838</t>
+          <t>64353</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>70838</t>
+          <t>64353</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>70838</t>
+          <t>64353</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>27682</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>17739</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>36240</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>31,15%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>19,96%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>40,78%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>23901</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>17052</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>35165</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>38,07%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>27,16%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>56,01%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>29601</t>
+          <t>19110</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19946</t>
+          <t>13376</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39888</t>
+          <t>24933</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>53502</t>
+          <t>46792</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39976</t>
+          <t>36173</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69126</t>
+          <t>58177</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>61189</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>52631</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>71132</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>68,85%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>59,22%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>80,04%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>38881</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>27617</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>45730</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>61,93%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>43,99%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>72,84%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>69428</t>
+          <t>39158</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59141</t>
+          <t>33335</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79083</t>
+          <t>44892</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>108309</t>
+          <t>100347</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>92685</t>
+          <t>88962</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>121835</t>
+          <t>110966</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,42%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>62782</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>62782</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>62782</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>58268</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>58268</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>58268</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>161811</t>
+          <t>147139</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>161811</t>
+          <t>147139</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>161811</t>
+          <t>147139</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
